--- a/7rmartSupermarket/src/test/resources/7rmartsupermarketlogin.xlsx
+++ b/7rmartSupermarket/src/test/resources/7rmartsupermarketlogin.xlsx
@@ -3,25 +3,39 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{A3CB3236-297E-4DEE-9EC3-6BC993B738DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sanar\Desktop\seleniumdocs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B8A69E5-4ED0-400A-9760-B8CCB407D24F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{510C5212-4B23-43D3-BEA4-94D435A433B9}"/>
+    <workbookView xWindow="2085" yWindow="1590" windowWidth="24420" windowHeight="11295" activeTab="1" xr2:uid="{510C5212-4B23-43D3-BEA4-94D435A433B9}"/>
   </bookViews>
   <sheets>
     <sheet name="supermarketlogin" sheetId="1" r:id="rId1"/>
+    <sheet name="adminuserlogin" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <oleSize ref="A1:U24"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="8">
   <si>
     <t>username</t>
   </si>
@@ -33,6 +47,18 @@
   </si>
   <si>
     <t>invalid</t>
+  </si>
+  <si>
+    <t>adminuser</t>
+  </si>
+  <si>
+    <t>adminpassword</t>
+  </si>
+  <si>
+    <t>reem_obsq</t>
+  </si>
+  <si>
+    <t>reem_pwd</t>
   </si>
 </sst>
 </file>
@@ -430,4 +456,34 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F47D2234-F14D-4000-965D-8DA5C1638D95}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>